--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -926,22 +926,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mjg4MDFlYjUtYzY5Ni00ZGYzLWExYTgtOTU2ZjljOWM0YTI1OjU3MDE2</t>
+          <t>MjJlZDgzYjItODM0OS00MDIxLWE5N2ItNTViZjUzZmJjNmNlOjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HYG0U31LZL</t>
+          <t>BKDLHOQUZX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Visita técnica - 90400888000142</t>
+          <t>Manutenção dobradiça 02.042.860.0001-13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Visita técnica, possível troca de sensor da porta</t>
+          <t>Referente a manutenção da dobradiça  da redutora</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -950,39 +950,35 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>850.76</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>850.76</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-01-29T14:37:35.560Z</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-01-22T14:57:37.000Z</t>
-        </is>
-      </c>
+          <t>2026-02-06T18:45:20.986Z</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Lucas Uenishi Tada</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-01-22T14:40:07.831Z</t>
+          <t>2026-01-30T18:45:35.907Z</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1003,74 +999,78 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>MzMzMDQ1Mjo1NzAxNg==</t>
+          <t>NDM1ODE3Nzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
+          <t>Mjg4MDFlYjUtYzY5Ni00ZGYzLWExYTgtOTU2ZjljOWM0YTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B1IJGVB5A</t>
+          <t>HYG0U31LZL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>R6IHIJPUZR</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Visita técnica - 90400888000142</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Visita técnica, possível troca de sensor da porta</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>350</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Cancelada</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2024-08-14T17:42:21.925Z</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>2026-01-29T14:37:35.560Z</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-01-22T14:57:37.000Z</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>IRACILDA LOPES</t>
+          <t>Lucas Uenishi Tada</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2024-08-07T17:45:02.123Z</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>ZDM4ZDY1NjMtN2E5Yy00ZDQ3LWFlMDktYzUwYzk4NDQ4NWY1OjU3MDE2</t>
-        </is>
-      </c>
+          <t>2026-01-22T14:40:07.831Z</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1088,82 +1088,74 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>MzMxMDM0OTo1NzAxNg==</t>
+          <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>canceled</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SKB8DXCYGE</t>
+          <t>B1IJGVB5A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dilmatec</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Diagnostico e resoluçao problema em 02 equipamentos que nao estavam atingindo temperatura</t>
-        </is>
-      </c>
+          <t>R6IHIJPUZR</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-09-04T15:24:13.519Z</t>
+          <t>2024-08-14T17:42:21.925Z</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Rafael Machado Barboza</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/2a7e8c69-1223-41d3-967d-474788d2fb01/signatures/51c1ade7-ff37-4ee9-b84d-46ee75381607.png</t>
-        </is>
-      </c>
+          <t>IRACILDA LOPES</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-08-28T15:35:41.479Z</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+          <t>2024-08-07T17:45:02.123Z</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>ZDM4ZDY1NjMtN2E5Yy00ZDQ3LWFlMDktYzUwYzk4NDQ4NWY1OjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1181,82 +1173,82 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzMxMDM0OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SKYBOA3Z-G</t>
+          <t>SKB8DXCYGE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FRANCESCO DE TOMMASO</t>
+          <t>Dilmatec</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
+          <t>Diagnostico e resoluçao problema em 02 equipamentos que nao estavam atingindo temperatura</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>988.85</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>988.85</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-09T21:20:29.860Z</t>
+          <t>2025-09-04T15:24:13.519Z</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Rafael Machado Barboza</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/2a7e8c69-1223-41d3-967d-474788d2fb01/signatures/51c1ade7-ff37-4ee9-b84d-46ee75381607.png</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-12-02T21:20:54.686Z</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-28T15:35:41.479Z</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1274,44 +1266,52 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>MzI2OTMyNjo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RYUVNWH3EG</t>
+          <t>SKYBOA3Z-G</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GARANTIA/61012019000142 - ASSOCIAÇÃO BRASILEIRA IJCSUD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>FRANCESCO DE TOMMASO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>988.85</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>988.85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-10-09T21:18:04.630Z</t>
+          <t>2025-12-09T21:20:29.860Z</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-10-02T21:19:25.794Z</t>
+          <t>2025-12-02T21:20:54.686Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>OGUzZjA5OGMtMTdlNy00MDY3LTllYjQtMzhmMWNhZGM4NjNmOjU3MDE2</t>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NDcxNTkzODo1NzAxNg==</t>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1371,36 +1371,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BKSEHUPHBG</t>
+          <t>RYUVNWH3EG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Manutenção dobradiça 02.042.860.0001-13</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Referente a manutenção da dobradiça  da redutora</t>
-        </is>
-      </c>
+          <t>GARANTIA/61012019000142 - ASSOCIAÇÃO BRASILEIRA IJCSUD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>850.76</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>850.76</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1410,23 +1406,27 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-01-27T19:18:07.101Z</t>
+          <t>2025-10-09T21:18:04.630Z</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Lucas Uenishi Tada</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-01-20T19:19:08.741Z</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
+          <t>2025-10-02T21:19:25.794Z</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>OGUzZjA5OGMtMTdlNy00MDY3LTllYjQtMzhmMWNhZGM4NjNmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NDM1ODE3Nzo1NzAxNg==</t>
+          <t>NDcxNTkzODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1456,78 +1456,62 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HJ0GXQO2EG</t>
+          <t>BKSEHUPHBG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JOANA DARC OLIVEIRA</t>
+          <t>Manutenção dobradiça 02.042.860.0001-13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Orçamento  para reforma de TFK 02 kg</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Reforma</t>
-        </is>
-      </c>
+          <t>Referente a manutenção da dobradiça  da redutora</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="b">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2167.29</t>
+          <t>850.76</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2167.29</t>
+          <t>850.76</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-10-06T13:42:48.402Z</t>
+          <t>2026-01-27T19:18:07.101Z</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Joana D’Arc Oliveira </t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/336279a3-e397-43dd-b3ef-8d0f677e97af/signatures/e23e6b48-ded8-4f36-a055-55d66d4bbb0d.png</t>
-        </is>
-      </c>
+          <t>Lucas Uenishi Tada</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-09-29T15:17:10.234Z</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2026-01-20T19:19:08.741Z</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1545,72 +1529,88 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>MzM3ODI5ODo1NzAxNg==</t>
+          <t>NDM1ODE3Nzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HYTE7IDHEX</t>
+          <t>HJ0GXQO2EG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MAQUINA 02</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+          <t>JOANA DARC OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Orçamento  para reforma de TFK 02 kg</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Reforma</t>
+        </is>
+      </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>979.73</t>
+          <t>2167.29</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>979.73</t>
+          <t>2167.29</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-10-06T18:41:42.725Z</t>
+          <t>2025-10-06T13:42:48.402Z</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joana D’Arc Oliveira </t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/336279a3-e397-43dd-b3ef-8d0f677e97af/signatures/e23e6b48-ded8-4f36-a055-55d66d4bbb0d.png</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2025-09-29T18:42:56.833Z</t>
+          <t>2025-09-29T15:17:10.234Z</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1630,29 +1630,29 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzM3ODI5ODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SYLVG8O3EG</t>
+          <t>HYTE7IDHEX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MAQUINA 01</t>
+          <t>MAQUINA 02</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>979.73</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>979.73</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-10-06T18:34:31.188Z</t>
+          <t>2025-10-06T18:41:42.725Z</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2025-09-29T18:38:37.635Z</t>
+          <t>2025-09-29T18:42:56.833Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1727,17 +1727,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BJFPMUNTXG</t>
+          <t>SYLVG8O3EG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MIX SOLUCOES AMBIENTAIS LTDA</t>
+          <t>MAQUINA 01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-10-15T21:09:42.233Z</t>
+          <t>2025-10-06T18:34:31.188Z</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1775,12 +1775,12 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2025-10-08T21:12:33.362Z</t>
+          <t>2025-09-29T18:38:37.635Z</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>OTUxMWZiNzEtYjliOC00NTg4LWE5MTAtZmI2ZmQxZmZlZmNlOjU3MDE2</t>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>NDgzNDc2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1812,37 +1812,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RJMEH3YZBX</t>
+          <t>BJFPMUNTXG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MAQUINA 1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Referente orçamento : NRLO2Z0E0001	TERRAFORM 5KG RECICLADORA DE RESIDUOS ORGANICOS          
- DATA DE COMPRA  13/01/2023</t>
-        </is>
-      </c>
+          <t>MIX SOLUCOES AMBIENTAIS LTDA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1016.75</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1016.75</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1852,7 +1847,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-19T15:56:33.655Z</t>
+          <t>2025-10-15T21:09:42.233Z</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1865,12 +1860,12 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2025-12-12T16:00:42.963Z</t>
+          <t>2025-10-08T21:12:33.362Z</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>OTYwNmY5MTktMmQxYi00NzI2LTg3MTYtZTJmMGE1MjE2NjFiOjU3MDE2</t>
+          <t>OTUxMWZiNzEtYjliOC00NTg4LWE5MTAtZmI2ZmQxZmZlZmNlOjU3MDE2</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1890,7 +1885,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>MzMxMDI2Nzo1NzAxNg==</t>
+          <t>NDgzNDc2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1902,123 +1897,128 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>RJMEH3YZBX</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MAQUINA 1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Referente orçamento : NRLO2Z0E0001	TERRAFORM 5KG RECICLADORA DE RESIDUOS ORGANICOS          
+ DATA DE COMPRA  13/01/2023</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1016.75</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1016.75</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2025-12-19T15:56:33.655Z</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-12-12T16:00:42.963Z</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>OTYwNmY5MTktMmQxYi00NzI2LTg3MTYtZTJmMGE1MjE2NjFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>MzMxMDI2Nzo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>NWQzZGY0ZDgtNDMyNS00ZDhlLWEwNDUtOGNlYjkxNzRmM2Y3OjU3MDE2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>RKDOWJG7-E</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>90400888000142 - BANCO SANTANDER (BRASIL) S/A</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>REFERENTE A VISITA TECNICA PARA DIAGNOSTICO 
 O VALOR PODE SER ALTERADO CASO PRECISE DE MAIS TEMPO PARA MANUNTENÇAO
 PEÇAS NAO ESTAO INCLUSAS NESTE ORÇAMENTO , CASO SEJA NECESSARIO, SERA ADICIONADO NO VALOR FINAL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2025-12-24T21:32:57.350Z</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-12-17T21:33:20.182Z</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>ODAxNDQ5MTMtNDYwMi00MjhmLWE1MWUtMWY1Y2I5NGIxY2Y1OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>MzMzMDQ1Mjo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SY9I6QSJBE</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>45246402000532 - CENTER NORTE S/A CONSTRUCA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>660.525</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>660.525</t>
+          <t>350</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-11-14T16:10:10.258Z</t>
+          <t>2025-12-24T21:32:57.350Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2041,12 +2041,12 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-11-07T16:26:09.914Z</t>
+          <t>2025-12-17T21:33:20.182Z</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
+          <t>ODAxNDQ5MTMtNDYwMi00MjhmLWE1MWUtMWY1Y2I5NGIxY2Y1OjU3MDE2</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NDE3MTYzNjo1NzAxNg==</t>
+          <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2078,36 +2078,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NjI1YjU4N2MtMmQ0My00OWRjLTlhMzEtZDk3MTlmNGM5NTk0OjU3MDE2</t>
+          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SJB-BNEZBL</t>
+          <t>SY9I6QSJBE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>71089640315 - MARCUS VINICIUS MORENO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>referente orçamento do raspador</t>
-        </is>
-      </c>
+          <t>45246402000532 - CENTER NORTE S/A CONSTRUCA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>138.57999999999998</t>
+          <t>660.525</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>138.57999999999998</t>
+          <t>660.525</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2117,7 +2113,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-15T20:05:35.735Z</t>
+          <t>2025-11-14T16:10:10.258Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2130,12 +2126,12 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-12-08T20:11:36.676Z</t>
+          <t>2025-11-07T16:26:09.914Z</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>M2EzOTI5YTItODc3Zi00NTJlLTk1NDktMmU5YWRiMWMwZmQ1OjU3MDE2</t>
+          <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2155,7 +2151,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>NDgzNTU4Mzo1NzAxNg==</t>
+          <t>NDE3MTYzNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2167,40 +2163,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NjI1YjU4N2MtMmQ0My00OWRjLTlhMzEtZDk3MTlmNGM5NTk0OjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BYCZRKIPEL</t>
+          <t>SJB-BNEZBL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>62730134620 - FRANCISCO DE LUCCA JUNIOR</t>
+          <t>71089640315 - MARCUS VINICIUS MORENO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GARANTIA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>garantia</t>
-        </is>
-      </c>
+          <t>referente orçamento do raspador</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>138.57999999999998</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>138.57999999999998</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2210,7 +2202,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-10-17T12:48:39.389Z</t>
+          <t>2025-12-15T20:05:35.735Z</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2223,12 +2215,12 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-10-10T13:07:18.487Z</t>
+          <t>2025-12-08T20:11:36.676Z</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
+          <t>M2EzOTI5YTItODc3Zi00NTJlLTk1NDktMmU5YWRiMWMwZmQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2248,7 +2240,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>NDgyMzMyODo1NzAxNg==</t>
+          <t>NDgzNTU4Mzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2260,27 +2252,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SYHCI3OLWE</t>
+          <t>BYCZRKIPEL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FRANCESCO DE TOMMASO</t>
+          <t>62730134620 - FRANCISCO DE LUCCA JUNIOR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+          <t>GARANTIA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+          <t>garantia</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2288,29 +2280,25 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-24T15:13:20.559Z</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-24T14:45:19.000Z</t>
-        </is>
-      </c>
+          <t>2025-10-17T12:48:39.389Z</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
@@ -2320,12 +2308,12 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-11-17T15:14:20.735Z</t>
+          <t>2025-10-10T13:07:18.487Z</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+          <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2345,122 +2333,219 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>MzI2OTMyNjo1NzAxNg==</t>
+          <t>NDgyMzMyODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SYHCI3OLWE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FRANCESCO DE TOMMASO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1047.65</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1047.65</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Recusada</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2025-11-24T15:13:20.559Z</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-24T14:45:19.000Z</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-11-17T15:14:20.735Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>SKD1SV5XZX</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>PREFEITURA MUNICIPAL DE ROSANA</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Referente a  transformação de 1 maquina composteira no valor total de R$ 3.000,00, de tensão 380V- trifasico, para 220V/trifasico. 
 As outras 02 são 220v</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="b">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="b">
         <v>0</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>2025-11-25T21:47:25.554Z</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
         <is>
           <t>2025-11-18T21:53:35.934Z</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>NjYwZjY1NTAtNjFmZS00N2NmLTlmZTktMzY2ZWVjNmViZGJmOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>NTgwMDkyOTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>HYS55O45GG</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2469,7 +2554,7 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2478,106 +2563,17 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2025-09-09T14:06:34.278Z</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:09:17.339Z</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SKRTB67OEL</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Salobo 2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2587,20 +2583,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-08-15T18:25:59.379Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-08-08T18:27:17.728Z</t>
+          <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2621,7 +2617,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2633,28 +2629,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NjdmNGZjZTctNzE3Yi00MGQyLThlMTctYWJhYzkwYmIwMjQwOjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BYMKBBIZWX</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PREFEITURA MUNICIPAL DE IBIUNA</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Referente a transformação de 1 maquina composteira no valor total de R$ 3.000,00, de tensão 380V- trifasico, para
-220V/trifasico.</t>
+          <t>Teste</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PREFEITURA MUNICIPAL DE IBIUNA</t>
+          <t>Teste</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2662,12 +2657,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2677,27 +2672,23 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-12-16T20:19:12.508Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-12-09T20:21:45.714Z</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>MzIyOGRmMDAtMThlNi00NTc3LTk2MzctYmVjM2QxYmZlOWYwOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:27:17.728Z</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2715,7 +2706,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>NTg1NDM3Nzo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2727,70 +2718,71 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
+          <t>NjdmNGZjZTctNzE3Yi00MGQyLThlMTctYWJhYzkwYmIwMjQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HJCRTZS--G</t>
+          <t>BYMKBBIZWX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>31415680817 - DOUGLAS HIROMITSU TFK 2Kg</t>
+          <t>PREFEITURA MUNICIPAL DE IBIUNA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Parafuso (Pino) que sustenta raspador quebrou, iremos fazer uma visita técnica para descobrir se há mais defeitos. 11 96619-3370</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>Referente a transformação de 1 maquina composteira no valor total de R$ 3.000,00, de tensão 380V- trifasico, para
+220V/trifasico.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PREFEITURA MUNICIPAL DE IBIUNA</t>
+        </is>
+      </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-12-08T12:21:25.404Z</t>
+          <t>2025-12-16T20:19:12.508Z</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>douglas simao</t>
-        </is>
-      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/6b2b07ff-cb70-450b-bc03-538da26b5fb0/signatures/82045e1d-cc6f-45af-a3f3-2c6a0906455d.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2025-12-01T12:28:02.404Z</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
+          <t>2025-12-09T20:21:45.714Z</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>MzIyOGRmMDAtMThlNi00NTc3LTk2MzctYmVjM2QxYmZlOWYwOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2808,34 +2800,34 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>NDUwNzM2Mzo1NzAxNg==</t>
+          <t>NTg1NDM3Nzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SJBLZ0HQLG</t>
+          <t>HJCRTZS--G</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OUTBACK MORUMBI</t>
+          <t>31415680817 - DOUGLAS HIROMITSU TFK 2Kg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Reforma de Estufa Airflow danificada</t>
+          <t>Parafuso (Pino) que sustenta raspador quebrou, iremos fazer uma visita técnica para descobrir se há mais defeitos. 11 96619-3370</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -2844,42 +2836,46 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>484</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-12-08T12:21:25.404Z</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>douglas simao</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/6b2b07ff-cb70-450b-bc03-538da26b5fb0/signatures/82045e1d-cc6f-45af-a3f3-2c6a0906455d.png</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-12-01T12:28:02.404Z</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2897,34 +2893,34 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDUwNzM2Mzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RKGEPXYF-E</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>60478583000192 - FUNDACAO ANGLO BRAS. DE EDUC. E CULT SP</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Referente orçamento : Composteira - St Pauls</t>
+          <t>Reforma de Estufa Airflow danificada</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -2933,12 +2929,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1756.6</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1756.6</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2948,7 +2944,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-12-11T14:05:43.837Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2961,12 +2957,12 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2025-12-04T15:21:12.082Z</t>
+          <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Y2NjZDRjMTgtOWYwOC00YjUwLWFiNzktOGU0NGNhZTQzMTg3OjU3MDE2</t>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2986,7 +2982,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>MzUzMTEwNTo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -2998,32 +2994,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B1VS7ID2GL</t>
+          <t>RKGEPXYF-E</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>60478583000192 - FUNDACAO ANGLO BRAS. DE EDUC. E CULT SP</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Referente orçamento : Composteira - St Pauls</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>1756.6</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>1756.6</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-10-06T18:43:16.449Z</t>
+          <t>2025-12-11T14:05:43.837Z</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3046,12 +3046,12 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2025-09-29T18:44:47.397Z</t>
+          <t>2025-12-04T15:21:12.082Z</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>Y2NjZDRjMTgtOWYwOC00YjUwLWFiNzktOGU0NGNhZTQzMTg3OjU3MDE2</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzUzMTEwNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OWI3NTBhMGYtMTViMS00MDg4LWJiZDMtYzI0MjI3Y2JhNTY3OjU3MDE2</t>
+          <t>MGM3OTczYTAtOWMwYS00YTUyLWI0NmEtZTVlNjZjYjNhMzc5OjU3MDE2</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3692,11 +3692,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mjg4MDFlYjUtYzY5Ni00ZGYzLWExYTgtOTU2ZjljOWM0YTI1OjU3MDE2</t>
+          <t>MjJlZDgzYjItODM0OS00MDIxLWE5N2ItNTViZjUzZmJjNmNlOjU3MDE2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3714,126 +3714,118 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Mjg4MDFlYjUtYzY5Ni00ZGYzLWExYTgtOTU2ZjljOWM0YTI1OjU3MDE2</t>
+          <t>MjJlZDgzYjItODM0OS00MDIxLWE5N2ItNTViZjUzZmJjNmNlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OTlhNzk3NzYtZGMzZC00MzBjLTlkY2MtNTQ4YzQ4MGE2YWQ1OjU3MDE2</t>
+          <t>NzJmM2MzNWEtNjRjMC00YjhmLTkyYWUtNTc0OTE0ZjMyNjgxOjU3MDE2</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>300</v>
+        <v>6325</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
+          <t>MjJlZDgzYjItODM0OS00MDIxLWE5N2ItNTViZjUzZmJjNmNlOjU3MDE2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NzQ3ZWZjY2YtNzk1MC00ZTI3LWI0NjItOTJmYWQ2YmQzOTY4OjU3MDE2</t>
+          <t>NTAzNjBhYjMtZTdhZC00NmIwLWFiNjYtMWJhNzZlNDgwMTFhOjU3MDE2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>600</v>
+        <v>6325</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
+          <t>MjJlZDgzYjItODM0OS00MDIxLWE5N2ItNTViZjUzZmJjNmNlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MTc3NWUyYTAtZjAxNy00NWQwLTg2ZTMtYWFiZjYzMzZhOWUzOjU3MDE2</t>
+          <t>OTM5OGMxMDAtYmM5Mi00MGRkLWJjN2ItOGE5NDY2MWUzOTJjOjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>680</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>2.001e+16</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MjJlZDgzYjItODM0OS00MDIxLWE5N2ItNTViZjUzZmJjNmNlOjU3MDE2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MTY1NGI0N2YtMTZmZS00OTljLWJhYTItYjk1ZDVkNjgwMDE4OjU3MDE2</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>680</v>
+        <v>2.001e+16</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MjJlZDgzYjItODM0OS00MDIxLWE5N2ItNTViZjUzZmJjNmNlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NGMwNTQyYWMtNGNjZC00NjljLThlZWItMDYxMjg2NzkzMmJhOjU3MDE2</t>
+          <t>OWRhOWRlMzktOTMxNy00ZjA4LWIwZDctYjBiZThlOWFhYTJjOjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>162</v>
       </c>
       <c r="C18" t="n">
-        <v>855</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MjJlZDgzYjItODM0OS00MDIxLWE5N2ItNTViZjUzZmJjNmNlOjU3MDE2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>855</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3842,21 +3834,21 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MjJlZDgzYjItODM0OS00MDIxLWE5N2ItNTViZjUzZmJjNmNlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mzc3ZTNkYTUtZTdkZC00YjBlLWFmMjEtMjhhMDkzNDk0YzY5OjU3MDE2</t>
+          <t>ZGY3YjY5NjMtODZmOS00OGNiLWFmNDItOTY1MjRhNGE3NmFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>18025</v>
+        <v>935</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
@@ -3864,16 +3856,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
+          <t>MjJlZDgzYjItODM0OS00MDIxLWE5N2ItNTViZjUzZmJjNmNlOjU3MDE2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>YjBiMDlkNmYtNGJmOS00NDEzLWE2N2QtM2JiNjY4MDk2ZmViOjU3MDE2</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>18025</v>
+        <v>4675</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3882,14 +3874,14 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
+          <t>MjJlZDgzYjItODM0OS00MDIxLWE5N2ItNTViZjUzZmJjNmNlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Njc1OGZkOTMtZmI5Ny00NDJiLWI1NzItOWE5OTYxYTgzMzE3OjU3MDE2</t>
+          <t>OWI3NTBhMGYtMTViMS00MDg4LWJiZDMtYzI0MjI3Y2JhNTY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -3898,18 +3890,22 @@
       <c r="C20" t="n">
         <v>350</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
+          <t>Mjg4MDFlYjUtYzY5Ni00ZGYzLWExYTgtOTU2ZjljOWM0YTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3917,83 +3913,87 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
+          <t>Mjg4MDFlYjUtYzY5Ni00ZGYzLWExYTgtOTU2ZjljOWM0YTI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZGZmZDFlYzMtNGE2Yi00YzFhLWI3YmYtM2Y5ZjBhMjhlMTIwOjU3MDE2</t>
+          <t>OTlhNzk3NzYtZGMzZC00MzBjLTlkY2MtNTQ4YzQ4MGE2YWQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1086</v>
+        <v>300</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
+          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
+          <t>NzQ3ZWZjY2YtNzk1MC00ZTI3LWI0NjItOTJmYWQ2YmQzOTY4OjU3MDE2</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1086</v>
+        <v>600</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
+          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ZjRkMzBkN2ItMTVhNC00MGI0LWI0N2MtYzcyM2QzM2U3ZDkyOjU3MDE2</t>
+          <t>MTc3NWUyYTAtZjAxNy00NWQwLTg2ZTMtYWFiZjYzMzZhOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>350</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>350</v>
+        <v>680</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -4002,25 +4002,25 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NGRlMTM3N2EtNzUwNC00YmUyLThmZjItMDQxZTc1ZDNjODRiOjU3MDE2</t>
+          <t>NGMwNTQyYWMtNGNjZC00NjljLThlZWItMDYxMjg2NzkzMmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>18025</v>
+        <v>855</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TROCADO EM GARANTIA</t>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -4028,60 +4028,56 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>18025</v>
+        <v>855</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NmQ1MDliODYtNGYyYy00YTNiLTk1YWEtYmM0MTZhNDBkNTY1OjU3MDE2</t>
+          <t>Mzc3ZTNkYTUtZTdkZC00YjBlLWFmMjEtMjhhMDkzNDk0YzY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>350</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TROCADO EM GARANTIA</t>
-        </is>
-      </c>
+        <v>18025</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>350</v>
+        <v>18025</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -4090,21 +4086,21 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MGEzNzZmYzEtYjUyNC00MjczLThkY2MtMDNjYjM3YjU5MmMxOjU3MDE2</t>
+          <t>Njc1OGZkOTMtZmI5Ny00NDJiLWI1NzItOWE5OTYxYTgzMzE3OjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>6325</v>
+        <v>350</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
@@ -4112,16 +4108,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>NTAzNjBhYjMtZTdhZC00NmIwLWFiNjYtMWJhNzZlNDgwMTFhOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6325</v>
+        <v>350</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -4130,65 +4126,61 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MTlkMmYxY2YtMGU1Yi00NWJjLWJjMzUtYjFmNmU1ZWExZWM5OjU3MDE2</t>
+          <t>ZGZmZDFlYzMtNGE2Yi00YzFhLWI3YmYtM2Y5ZjBhMjhlMTIwOjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>350</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
+        <v>1086</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
         <v>6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>350</v>
+        <v>1086</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OWYyNjNiMzItMjQyNy00ZDdlLThiMDMtZmE2NWQzZTdiY2IyOjU3MDE2</t>
+          <t>ZjRkMzBkN2ItMTVhNC00MGI0LWI0N2MtYzcyM2QzM2U3ZDkyOjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>2.001e+16</v>
+        <v>350</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
@@ -4196,96 +4188,104 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MTY1NGI0N2YtMTZmZS00OTljLWJhYTItYjk1ZDVkNjgwMDE4OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2.001e+16</v>
+        <v>350</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>YzAwZDljYWMtZTZlZS00YzhjLTlkMDEtMjBkMmFmMTVkMTdkOjU3MDE2</t>
+          <t>NGRlMTM3N2EtNzUwNC00YmUyLThmZjItMDQxZTc1ZDNjODRiOjU3MDE2</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>162</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>324</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+        <v>18025</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TROCADO EM GARANTIA</t>
+        </is>
+      </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>18025</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ZmNkYTljNGItMDY5ZS00Mzk0LThlODktYmQ4YzkxOWUyNTAzOjU3MDE2</t>
+          <t>NmQ1MDliODYtNGYyYy00YTNiLTk1YWEtYmM0MTZhNDBkNTY1OjU3MDE2</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>935</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TROCADO EM GARANTIA</t>
+        </is>
+      </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>YjBiMDlkNmYtNGJmOS00NDEzLWE2N2QtM2JiNjY4MDk2ZmViOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4675</v>
+        <v>350</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4294,38 +4294,38 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MDFmODQ2OWUtMmMyMC00NzEwLWE4NTEtMmFkOWFjYjRlYjQ2OjU3MDE2</t>
+          <t>MGEzNzZmYzEtYjUyNC00MjczLThkY2MtMDNjYjM3YjU5MmMxOjU3MDE2</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>50</v>
+        <v>6325</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>NDUwZmFlOTEtODg1My00ZTcwLWIwOTgtZWM2Nzc3MzgzNjgyOjU3MDE2</t>
+          <t>NTAzNjBhYjMtZTdhZC00NmIwLWFiNjYtMWJhNzZlNDgwMTFhOjU3MDE2</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>50</v>
+        <v>6325</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4334,78 +4334,82 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MjhmNDNmYjAtZjgzMi00MThiLWEyNTAtZWVlODc0ZjQxYzliOjU3MDE2</t>
+          <t>MTlkMmYxY2YtMGU1Yi00NWJjLWJjMzUtYjFmNmU1ZWExZWM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>1365</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E31" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1365</v>
+        <v>350</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MmQyOGU2OWYtM2IzOS00ZjYwLWJmYTctYmViYTY2M2UxNzdjOjU3MDE2</t>
+          <t>OWYyNjNiMzItMjQyNy00ZDdlLThiMDMtZmE2NWQzZTdiY2IyOjU3MDE2</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>375</v>
+        <v>2.001e+16</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>MTY1NGI0N2YtMTZmZS00OTljLWJhYTItYjk1ZDVkNjgwMDE4OjU3MDE2</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>375</v>
+        <v>2.001e+16</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -4414,101 +4418,101 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MzVjNDRmYjctMTI1My00NDg3LThlNmUtOWZhN2YyYWMyNjg3OjU3MDE2</t>
+          <t>YzAwZDljYWMtZTZlZS00YzhjLTlkMDEtMjBkMmFmMTVkMTdkOjU3MDE2</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>162</v>
       </c>
       <c r="C33" t="n">
-        <v>1.152e+16</v>
+        <v>324</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>NDM0MjA4NTAtZjAwOC00YzMyLWJlM2QtODFlMzljMjE0OTk4OjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.152e+16</v>
+        <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NDNkMGNjZmMtMjFmMS00NjQyLWI4OWYtYTk4ODg2NjkxMjcwOjU3MDE2</t>
+          <t>ZmNkYTljNGItMDY5ZS00Mzk0LThlODktYmQ4YzkxOWUyNTAzOjU3MDE2</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>168</v>
+        <v>935</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+          <t>YjBiMDlkNmYtNGJmOS00NDEzLWE2N2QtM2JiNjY4MDk2ZmViOjU3MDE2</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>4675</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzJiYTY3MzAtNDNmOS00MjFmLTkwYzEtYzI0MDJiM2QzZWMzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NDRlYzI5NjAtMTZmYi00MzM3LWEzZTEtNGJmOTg0Y2Y1MzFhOjU3MDE2</t>
+          <t>MDFmODQ2OWUtMmMyMC00NzEwLWE4NTEtMmFkOWFjYjRlYjQ2OjU3MDE2</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>700</v>
+        <v>50</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
@@ -4521,15 +4525,15 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>NDUwZmFlOTEtODg1My00ZTcwLWIwOTgtZWM2Nzc3MzgzNjgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>350</v>
+        <v>50</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4541,14 +4545,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>N2NjNjliYTAtNTVlZi00NjNmLThkMmUtZGMzYzIyZjRhM2FiOjU3MDE2</t>
+          <t>MjhmNDNmYjAtZjgzMi00MThiLWEyNTAtZWVlODc0ZjQxYzliOjU3MDE2</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>350</v>
+        <v>1365</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
@@ -4561,11 +4565,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>350</v>
+        <v>1365</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -4581,14 +4585,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OTg0ZDY5MWUtZTJiZS00NmM0LTg1OGMtNDQ1ZTMwMmY2MWE3OjU3MDE2</t>
+          <t>MmQyOGU2OWYtM2IzOS00ZjYwLWJmYTctYmViYTY2M2UxNzdjOjU3MDE2</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
@@ -4601,11 +4605,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -4621,14 +4625,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OWRkMWJkNWQtMjE5Yy00OTY0LWExNzYtZTI4YzkyN2Q4ODdlOjU3MDE2</t>
+          <t>MzVjNDRmYjctMTI1My00NDg3LThlNmUtOWZhN2YyYWMyNjg3OjU3MDE2</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>72</v>
+        <v>1.152e+16</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
@@ -4641,11 +4645,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Y2FjZGRiY2YtOTQ5NS00NDIyLWE4ODctYjk4ZGUxNjU1MzMyOjU3MDE2</t>
+          <t>NDM0MjA4NTAtZjAwOC00YzMyLWJlM2QtODFlMzljMjE0OTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>18</v>
+        <v>1.152e+16</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4661,14 +4665,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>YTAxNDZjNzgtMDljZi00ZGQ4LTkwOTItZmM5N2QyNzM3MGEwOjU3MDE2</t>
+          <t>NDNkMGNjZmMtMjFmMS00NjQyLWI4OWYtYTk4ODg2NjkxMjcwOjU3MDE2</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="C39" t="n">
-        <v>18025</v>
+        <v>168</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
@@ -4681,15 +4685,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>18025</v>
+        <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4701,14 +4705,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>YTM1YmFkNmQtN2EzNS00Njk0LTliNTMtNmZiMjAwNzQ5NzFkOjU3MDE2</t>
+          <t>NDRlYzI5NjAtMTZmYi00MzM3LWEzZTEtNGJmOTg0Y2Y1MzFhOjU3MDE2</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>25625</v>
+        <v>700</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
@@ -4721,15 +4725,15 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MTdjYWQ5ZTAtMmQ3YS00OTM0LWIyOGEtYzMxYjY1ODZkNDIzOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>25625</v>
+        <v>350</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4741,14 +4745,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>YzFlYTExODctMmJkNy00N2RhLThiMTQtZTVjMTY0NWY1Y2Y5OjU3MDE2</t>
+          <t>N2NjNjliYTAtNTVlZi00NjNmLThkMmUtZGMzYzIyZjRhM2FiOjU3MDE2</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>182225</v>
+        <v>350</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
@@ -4761,11 +4765,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>OWU3NmYwYWEtZWNhZi00YTBiLWE2NTUtNjE5NTkwNDIwZDNjOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>182225</v>
+        <v>350</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4781,14 +4785,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>YzRiYzAxZjEtOWY2Zi00ZWQ0LWJmMjgtZmYxY2RjNjY1OTBiOjU3MDE2</t>
+          <t>OTg0ZDY5MWUtZTJiZS00NmM0LTg1OGMtNDQ1ZTMwMmY2MWE3OjU3MDE2</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>9940000000000000</v>
+        <v>85</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
@@ -4801,11 +4805,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>OWMxNWU5ZjUtOWI3Ny00ZmYyLWExMWYtM2RkYzA3ZWFjYzU5OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>9940000000000000</v>
+        <v>85</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4821,14 +4825,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ZGMxMDhlMDAtNmY3Ni00OWE1LTg0MDMtZjVmNjUyZGVkNzZlOjU3MDE2</t>
+          <t>OWRkMWJkNWQtMjE5Yy00OTY0LWExNzYtZTI4YzkyN2Q4ODdlOjU3MDE2</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C43" t="n">
-        <v>2073</v>
+        <v>72</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
@@ -4841,11 +4845,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>Y2FjZGRiY2YtOTQ5NS00NDIyLWE4ODctYjk4ZGUxNjU1MzMyOjU3MDE2</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2073</v>
+        <v>18</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4861,14 +4865,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ZjczNzc1Y2UtNGU2Mi00NGEzLTk5NWUtYzRlZmRjMzFhMTI2OjU3MDE2</t>
+          <t>YTAxNDZjNzgtMDljZi00ZGQ4LTkwOTItZmM5N2QyNzM3MGEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>36</v>
+        <v>18025</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
@@ -4881,11 +4885,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ZmQ5YTY2ZWEtZDM4NS00MWMwLWI0NWYtODI3ZjAxNzRjNzE1OjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>9</v>
+        <v>18025</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4901,14 +4905,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ZmQ3OWNiYjEtZmY3Yi00MjVkLWJhODgtYjA3NjQyZWY1MzYwOjU3MDE2</t>
+          <t>YTM1YmFkNmQtN2EzNS00Njk0LTliNTMtNmZiMjAwNzQ5NzFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>1578</v>
+        <v>25625</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
@@ -4921,11 +4925,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Y2I2NzA1MTItNDc5NS00ZWVmLWJkOTktY2JlZmJiZTNmNTFlOjU3MDE2</t>
+          <t>MTdjYWQ5ZTAtMmQ3YS00OTM0LWIyOGEtYzMxYjY1ODZkNDIzOjU3MDE2</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1578</v>
+        <v>25625</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4941,71 +4945,71 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MTE0NDUwMGUtM2ZiMi00OWQ1LWFmY2EtMzNjNzZmNjBhMTVmOjU3MDE2</t>
+          <t>YzFlYTExODctMmJkNy00N2RhLThiMTQtZTVjMTY0NWY1Y2Y5OjU3MDE2</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>350</v>
+        <v>182225</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>OWU3NmYwYWEtZWNhZi00YTBiLWE2NTUtNjE5NTkwNDIwZDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>350</v>
+        <v>182225</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NWM5YzAxYzktMTIwMS00ZjhkLWJjOGMtN2U3NDlmOTlmMzRkOjU3MDE2</t>
+          <t>YzRiYzAxZjEtOWY2Zi00ZWQ0LWJmMjgtZmYxY2RjNjY1OTBiOjU3MDE2</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>85</v>
+        <v>9940000000000000</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>OWMxNWU5ZjUtOWI3Ny00ZmYyLWExMWYtM2RkYzA3ZWFjYzU5OjU3MDE2</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>85</v>
+        <v>9940000000000000</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -5014,38 +5018,38 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NjRmMDVhODItNmU2Mi00ZDRhLTk5NmItNzM2ODI0YjE2MjRmOjU3MDE2</t>
+          <t>ZGMxMDhlMDAtNmY3Ni00OWE1LTg0MDMtZjVmNjUyZGVkNzZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>1365</v>
+        <v>2073</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1365</v>
+        <v>2073</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5054,38 +5058,38 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OGUzMjVkZDYtOTA3Yi00MjFjLWFjYzgtOWVlMGI3MjJkNjIzOjU3MDE2</t>
+          <t>ZjczNzc1Y2UtNGU2Mi00NGEzLTk5NWUtYzRlZmRjMzFhMTI2OjU3MDE2</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>350</v>
+        <v>36</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>ZmQ5YTY2ZWEtZDM4NS00MWMwLWI0NWYtODI3ZjAxNzRjNzE1OjU3MDE2</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>350</v>
+        <v>9</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5094,38 +5098,38 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Yjk2YzIwMDktMzVkMy00ZGRjLWIwOTYtOTJjOWFlMjZiM2FhOjU3MDE2</t>
+          <t>ZmQ3OWNiYjEtZmY3Yi00MjVkLWJhODgtYjA3NjQyZWY1MzYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>375</v>
+        <v>1578</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>Y2I2NzA1MTItNDc5NS00ZWVmLWJkOTktY2JlZmJiZTNmNTFlOjU3MDE2</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>375</v>
+        <v>1578</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5134,21 +5138,21 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ZTA0MDdkOTgtNjJjMi00ZTgyLWFmMzEtYzg4MzdkYzhjYmMzOjU3MDE2</t>
+          <t>MTE0NDUwMGUtM2ZiMi00OWQ1LWFmY2EtMzNjNzZmNjBhMTVmOjU3MDE2</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
@@ -5161,15 +5165,15 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5181,31 +5185,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MDhmZjQ1YWQtNTY2Yi00YTlkLWIyMWEtZDI5Y2RkYThlODAwOjU3MDE2</t>
+          <t>NWM5YzAxYzktMTIwMS00ZjhkLWJjOGMtN2U3NDlmOTlmMzRkOjU3MDE2</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5214,38 +5218,38 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>N2EyYTQzZjktNzgxZi00Mzk2LWEyNzMtODM0NmViMTE4MWE2OjU3MDE2</t>
+          <t>NjRmMDVhODItNmU2Mi00ZDRhLTk5NmItNzM2ODI0YjE2MjRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>85</v>
+        <v>1365</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>85</v>
+        <v>1365</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5254,34 +5258,34 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OWIyYjYwOTktYTg5MC00ZjRhLWEzOGMtNDI3YTE2MTA1NTI1OjU3MDE2</t>
+          <t>OGUzMjVkZDYtOTA3Yi00MjFjLWFjYzgtOWVlMGI3MjJkNjIzOjU3MDE2</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -5289,19 +5293,19 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>YTJjM2ExNTAtOWExYi00Mzk1LWE1N2MtM2JkYTU3MDBiMzhlOjU3MDE2</t>
+          <t>Yjk2YzIwMDktMzVkMy00ZGRjLWIwOTYtOTJjOWFlMjZiM2FhOjU3MDE2</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -5312,11 +5316,11 @@
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5334,38 +5338,38 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>YTYxMjU3ODEtZjY4ZS00MDQyLTg5YmItYzg1YTA3YTdmZmY5OjU3MDE2</t>
+          <t>ZTA0MDdkOTgtNjJjMi00ZTgyLWFmMzEtYzg4MzdkYzhjYmMzOjU3MDE2</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>350</v>
+        <v>2073</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>350</v>
+        <v>2073</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -5374,21 +5378,21 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>YTg1ZmQyOGMtNDZkOC00YTgwLWJhODUtOGI5OTA5ZDliZjg1OjU3MDE2</t>
+          <t>MDhmZjQ1YWQtNTY2Yi00YTlkLWIyMWEtZDI5Y2RkYThlODAwOjU3MDE2</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>8399999999999999</v>
+        <v>9</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
@@ -5401,11 +5405,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>8399999999999999</v>
+        <v>9</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -5421,14 +5425,14 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>YTlhNDQ1NWItMWI4OS00ZGM0LThiOTgtMzZlOTcxNTE0NzcyOjU3MDE2</t>
+          <t>N2EyYTQzZjktNzgxZi00Mzk2LWEyNzMtODM0NmViMTE4MWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>2073</v>
+        <v>85</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
@@ -5441,11 +5445,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2073</v>
+        <v>85</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -5461,14 +5465,14 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ZTZmYzJiNjEtYzBjNS00NjM2LWI0YmEtNzZlMGE1NWI2ODIwOjU3MDE2</t>
+          <t>OWIyYjYwOTktYTg5MC00ZjRhLWEzOGMtNDI3YTE2MTA1NTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>2502</v>
+        <v>700</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
@@ -5481,15 +5485,15 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2502</v>
+        <v>350</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5501,14 +5505,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ZWQ1NDY3MTUtZjAxMC00OTM2LTljZDctNzBmMjRlZjVhYTQwOjU3MDE2</t>
+          <t>YTJjM2ExNTAtOWExYi00Mzk1LWE1N2MtM2JkYTU3MDBiMzhlOjU3MDE2</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>6325</v>
+        <v>375</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
@@ -5521,11 +5525,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>6325</v>
+        <v>375</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -5541,31 +5545,31 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NjA1ZWIxZDMtNWMxMC00NGE2LWEzZjEtYTZkZjM1MWVhNjQwOjU3MDE2</t>
+          <t>YTYxMjU3ODEtZjY4ZS00MDQyLTg5YmItYzg1YTA3YTdmZmY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>1793</v>
+        <v>350</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>NjdjMzI5NDAtMmU1Mi00MjQ1LTgxNGQtNjUyNWI3ZTQyNDU4OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1793</v>
+        <v>350</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5574,82 +5578,78 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OTFkMjc2ZDEtOTkxOC00OGZlLWEyMWYtZGEwNDg3MDFiNzkxOjU3MDE2</t>
+          <t>YTg1ZmQyOGMtNDZkOC00YTgwLWJhODUtOGI5OTA5ZDliZjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>350</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
+        <v>8399999999999999</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>350</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>YTlhMGVhYzMtYjJhZS00OWUwLTg5YWQtNjdjYzIyMWUyZDZmOjU3MDE2</t>
+          <t>YTlhNDQ1NWItMWI4OS00ZGM0LThiOTgtMzZlOTcxNTE0NzcyOjU3MDE2</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>2841</v>
+        <v>2073</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MGQ3YTYzZmEtOGQyZS00YWNiLTljMWYtNTNiM2JkMzRmOTYwOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2841</v>
+        <v>2073</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5658,38 +5658,38 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>N2Y4YTcwY2UtZTQxOC00NjhlLTkwMTUtZjgzYTQzNzY2ZjczOjU3MDE2</t>
+          <t>ZTZmYzJiNjEtYzBjNS00NjM2LWI0YmEtNzZlMGE1NWI2ODIwOjU3MDE2</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>18025</v>
+        <v>2502</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>18025</v>
+        <v>2502</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5698,38 +5698,38 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OTg5NzBmYjAtNTRjNC00ZjYyLWE3MGItNTMzZWE5MWY3Y2Y0OjU3MDE2</t>
+          <t>ZWQ1NDY3MTUtZjAxMC00OTM2LTljZDctNzBmMjRlZjVhYTQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>350</v>
+        <v>6325</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>350</v>
+        <v>6325</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5738,38 +5738,38 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>YTQxNGE2YzgtNzhlMi00ZThlLWE4N2UtM2MzYzQ3NDIxYzFkOjU3MDE2</t>
+          <t>NjA1ZWIxZDMtNWMxMC00NGE2LWEzZjEtYTZkZjM1MWVhNjQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>1365</v>
+        <v>1793</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+          <t>NjdjMzI5NDAtMmU1Mi00MjQ1LTgxNGQtNjUyNWI3ZTQyNDU4OjU3MDE2</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1365</v>
+        <v>1793</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5778,14 +5778,14 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>YjNiZjVjNTEtZDg3NC00ZjMyLWI4MjgtNjVkZTJjN2IwNDRkOjU3MDE2</t>
+          <t>OTFkMjc2ZDEtOTkxOC00OGZlLWEyMWYtZGEwNDg3MDFiNzkxOjU3MDE2</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -5794,18 +5794,22 @@
       <c r="C67" t="n">
         <v>350</v>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -5818,82 +5822,78 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MmUwOWMzZjUtNzljZS00OTZhLWExMTQtMDNhNTZlMmMxZDViOjU3MDE2</t>
+          <t>YTlhMGVhYzMtYjJhZS00OWUwLTg5YWQtNjdjYzIyMWUyZDZmOjU3MDE2</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>350</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
+        <v>2841</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NWQzZGY0ZDgtNDMyNS00ZDhlLWEwNDUtOGNlYjkxNzRmM2Y3OjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>MGQ3YTYzZmEtOGQyZS00YWNiLTljMWYtNTNiM2JkMzRmOTYwOjU3MDE2</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>350</v>
+        <v>2841</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>NWQzZGY0ZDgtNDMyNS00ZDhlLWEwNDUtOGNlYjkxNzRmM2Y3OjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>YmUzOThhOTAtNGYyYi00YmViLWJmYzUtNDJmYTA2NDg0OGRhOjU3MDE2</t>
+          <t>N2Y4YTcwY2UtZTQxOC00NjhlLTkwMTUtZjgzYTQzNzY2ZjczOjU3MDE2</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>660525</v>
+        <v>18025</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
+          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MGY5YWI3Y2UtNWJiMC00ZWMwLTgyZjktNzU4Zjc0YmUyZDg3OjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>660525</v>
+        <v>18025</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5902,38 +5902,38 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
+          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NzhmYWJiYmYtYmMxNi00NGJiLWE1YmItMTUwOWU3ZjhhMDI5OjU3MDE2</t>
+          <t>OTg5NzBmYjAtNTRjNC00ZjYyLWE3MGItNTMzZWE5MWY3Y2Y0OjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NjI1YjU4N2MtMmQ0My00OWRjLTlhMzEtZDk3MTlmNGM5NTk0OjU3MDE2</t>
+          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MWE3ZTVjNzMtNWE5Ny00NmMxLWE3MDMtNzVjOTA4ZDU1ODg5OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5942,38 +5942,38 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>NjI1YjU4N2MtMmQ0My00OWRjLTlhMzEtZDk3MTlmNGM5NTk0OjU3MDE2</t>
+          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>YjUzMDQzOGYtNTZlNi00NTZhLTg4YWEtYjgyZjdhNTA3OWVhOjU3MDE2</t>
+          <t>YTQxNGE2YzgtNzhlMi00ZThlLWE4N2UtM2MzYzQ3NDIxYzFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>5858</v>
+        <v>1365</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NjI1YjU4N2MtMmQ0My00OWRjLTlhMzEtZDk3MTlmNGM5NTk0OjU3MDE2</t>
+          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>43</v>
+        <v>1365</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>NjI1YjU4N2MtMmQ0My00OWRjLTlhMzEtZDk3MTlmNGM5NTk0OjU3MDE2</t>
+          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MjA0Mzk0M2ItOWI2Ni00Y2NkLWJlNjgtOTUwNjdmMjVkM2Y3OjU3MDE2</t>
+          <t>YjNiZjVjNTEtZDg3NC00ZjMyLWI4MjgtNjVkZTJjN2IwNDRkOjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -6000,16 +6000,16 @@
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -6017,83 +6017,87 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NTk3Mjg1M2YtM2Q1MS00NmY0LWE3YjgtYzc0YWZjMWM0NzZlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NDUwYmZhOGUtMTA3Ni00MmY2LWFhMjgtNWY5YzNmNzMzMWQ1OjU3MDE2</t>
+          <t>MmUwOWMzZjUtNzljZS00OTZhLWExMTQtMDNhNTZlMmMxZDViOjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>18025</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NWQzZGY0ZDgtNDMyNS00ZDhlLWEwNDUtOGNlYjkxNzRmM2Y3OjU3MDE2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>18025</v>
+        <v>350</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NWQzZGY0ZDgtNDMyNS00ZDhlLWEwNDUtOGNlYjkxNzRmM2Y3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MTY2NjMxNTAtYWUyMi00YzY2LTgwNDYtYTkzZTgzODgxNGQ4OjU3MDE2</t>
+          <t>YmUzOThhOTAtNGYyYi00YmViLWJmYzUtNDJmYTA2NDg0OGRhOjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>350</v>
+        <v>660525</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MGY5YWI3Y2UtNWJiMC00ZWMwLTgyZjktNzU4Zjc0YmUyZDg3OjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>350</v>
+        <v>660525</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6102,38 +6106,38 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MWM2N2JjOTQtYTFlYy00YjM5LTg5MjctNThkNjNhNGVkNWRkOjU3MDE2</t>
+          <t>NzhmYWJiYmYtYmMxNi00NGJiLWE1YmItMTUwOWU3ZjhhMDI5OjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>1086</v>
+        <v>80</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjI1YjU4N2MtMmQ0My00OWRjLTlhMzEtZDk3MTlmNGM5NTk0OjU3MDE2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
+          <t>MWE3ZTVjNzMtNWE5Ny00NmMxLWE3MDMtNzVjOTA4ZDU1ODg5OjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1086</v>
+        <v>80</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -6142,78 +6146,78 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjI1YjU4N2MtMmQ0My00OWRjLTlhMzEtZDk3MTlmNGM5NTk0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NjYzOTVlNjEtODVjOC00YmY4LTljNjEtODljNGZjNDM5OWY2OjU3MDE2</t>
+          <t>YjUzMDQzOGYtNTZlNi00NTZhLTg4YWEtYjgyZjdhNTA3OWVhOjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>350</v>
+        <v>5858</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjI1YjU4N2MtMmQ0My00OWRjLTlhMzEtZDk3MTlmNGM5NTk0OjU3MDE2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>350</v>
+        <v>43</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjI1YjU4N2MtMmQ0My00OWRjLTlhMzEtZDk3MTlmNGM5NTk0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NmY5NWU4YjctMTU4NC00NzJiLTgwODctMjkyYjg3NGY5ODU3OjU3MDE2</t>
+          <t>MjA0Mzk0M2ItOWI2Ni00Y2NkLWJlNjgtOTUwNjdmMjVkM2Y3OjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>3795</v>
+        <v>350</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>3795</v>
+        <v>350</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6222,14 +6226,14 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Yzg5MTQ4NTgtZjZhZS00M2VjLWI2OGItNGY0ZTA3YzYwM2E4OjU3MDE2</t>
+          <t>NDUwYmZhOGUtMTA3Ni00MmY2LWFhMjgtNWY5YzNmNzMzMWQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -6240,11 +6244,11 @@
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6262,21 +6266,21 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ZGI4ODAzMmQtZTAzYS00YmQ5LWJmMjUtNjk1ZGUwODliNzI1OjU3MDE2</t>
+          <t>MTY2NjMxNTAtYWUyMi00YzY2LTgwNDYtYTkzZTgzODgxNGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>1.68e+16</v>
+        <v>350</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
@@ -6289,11 +6293,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2.1e+16</v>
+        <v>350</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6309,14 +6313,14 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ZjQ5NjJjZjctN2U2ZS00ZWE3LTkwY2ItZWIxNjFlODE2YzNkOjU3MDE2</t>
+          <t>MWM2N2JjOTQtYTFlYy00YjM5LTg5MjctNThkNjNhNGVkNWRkOjU3MDE2</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>4050000000000001</v>
+        <v>1086</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
@@ -6329,11 +6333,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>4050000000000001</v>
+        <v>1086</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -6349,35 +6353,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MzkwMmU1MjMtZGQ5ZC00ZjEzLWIxZjItNTM4MThiODRhODY0OjU3MDE2</t>
+          <t>NjYzOTVlNjEtODVjOC00YmY4LTljNjEtODljNGZjNDM5OWY2OjU3MDE2</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Transformaçao 380V- trifasico, para 220V/trifasico</t>
-        </is>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>NDk0NTM0YTgtOGM0MC00ZTYwLWJhNDAtMzMxNDRiZjA3ZGY4OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>3000</v>
+        <v>350</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -6386,23 +6386,227 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>NmY5NWU4YjctMTU4NC00NzJiLTgwODctMjkyYjg3NGY5ODU3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="n">
+        <v>3795</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="n">
+        <v>8</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>3795</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Yzg5MTQ4NTgtZjZhZS00M2VjLWI2OGItNGY0ZTA3YzYwM2E4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>18025</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="n">
+        <v>8</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>18025</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ZGI4ODAzMmQtZTAzYS00YmQ5LWJmMjUtNjk1ZGUwODliNzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>8</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1.68e+16</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="n">
+        <v>8</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ZjQ5NjJjZjctN2U2ZS00ZWE3LTkwY2ItZWIxNjFlODE2YzNkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4050000000000001</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="n">
+        <v>8</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>4050000000000001</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MzkwMmU1MjMtZGQ5ZC00ZjEzLWIxZjItNTM4MThiODRhODY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Transformaçao 380V- trifasico, para 220V/trifasico</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>NDk0NTM0YTgtOGM0MC00ZTYwLWJhNDAtMzMxNDRiZjA3ZGY4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" t="n">
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="n">
         <v>1700</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -6410,258 +6614,258 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E82" t="n">
+      <c r="E87" t="n">
         <v>2</v>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H82" t="n">
+      <c r="H87" t="n">
         <v>1700</v>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>1</v>
-      </c>
-      <c r="C83" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="n">
-        <v>2</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H83" t="n">
-        <v>47370</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>ODcyMmI3MTgtOTQ2ZC00NDhiLWEwMjctOWFlZDc4NjQ1Y2ZhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Transformaçao 380V- trifasico, para 220V/trifasico</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>2</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>NjdmNGZjZTctNzE3Yi00MGQyLThlMTctYWJhYzkwYmIwMjQwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>NDk0NTM0YTgtOGM0MC00ZTYwLWJhNDAtMzMxNDRiZjA3ZGY4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H84" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>NjdmNGZjZTctNzE3Yi00MGQyLThlMTctYWJhYzkwYmIwMjQwOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>NzVmMDU4ODAtZTJiMi00MmFlLTgzZmItYTJlYmYwY2EyNTgxOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>67</v>
-      </c>
-      <c r="C85" t="n">
-        <v>134</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>67Km de distancia</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>3</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>2</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>ZDQ0NDkzNjgtNjE2MS00YjRkLWEyNWUtOTdkOGFiMjFiMjVjOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" t="n">
-        <v>350</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Visita técnica</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>3</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>NWVmNmQ0MDEtNzBmMy00Yzg3LWFlZDAtYzJiYTM1MTc4OWNlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H86" t="n">
-        <v>350</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="n">
-        <v>3</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ODcyMmI3MTgtOTQ2ZC00NDhiLWEwMjctOWFlZDc4NjQ1Y2ZhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Transformaçao 380V- trifasico, para 220V/trifasico</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>NjdmNGZjZTctNzE3Yi00MGQyLThlMTctYWJhYzkwYmIwMjQwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>NDk0NTM0YTgtOGM0MC00ZTYwLWJhNDAtMzMxNDRiZjA3ZGY4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>NjdmNGZjZTctNzE3Yi00MGQyLThlMTctYWJhYzkwYmIwMjQwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NzVmMDU4ODAtZTJiMi00MmFlLTgzZmItYTJlYmYwY2EyNTgxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>67</v>
+      </c>
+      <c r="C90" t="n">
+        <v>134</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>67Km de distancia</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ZDQ0NDkzNjgtNjE2MS00YjRkLWEyNWUtOTdkOGFiMjFiMjVjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>350</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Visita técnica</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>NWVmNmQ0MDEtNzBmMy00Yzg3LWFlZDAtYzJiYTM1MTc4OWNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>350</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="n">
+        <v>3</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" t="n">
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="n">
         <v>494677</v>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -6679,244 +6883,44 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E88" t="n">
+      <c r="E93" t="n">
         <v>3</v>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H88" t="n">
+      <c r="H93" t="n">
         <v>494677</v>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>MTU2MjFmZWMtYWZjYi00MTg4LThjMmItNTM5ZWExYmYyYjM2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" t="n">
-        <v>350</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="n">
-        <v>10</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>MzYyZjJjODUtNDVjYS00NmU3LWEwYzUtMzhmZDc3ZjM5NTc0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H89" t="n">
-        <v>350</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>MjdkOWFjYmEtM2RiMi00NjA5LWE5ZjQtMDc0MmQyOThiNzk5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>20</v>
-      </c>
-      <c r="C90" t="n">
-        <v>168</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="n">
-        <v>10</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>MWU3ZGQ4MmMtYTg0Zi00ZDM2LWIxNDgtNjBhZDljYjYwZTliOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H90" t="n">
-        <v>8400000000000001</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Mzk5MTdiNmEtZmE3Ni00NWExLWFiODctOTIwNTY4YmViNGMwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>2</v>
-      </c>
-      <c r="C91" t="n">
-        <v>190</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="n">
-        <v>10</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>OGEzODdhOTUtNmU2Ni00NWQ0LWFhMzgtNzQzMGI2MWY4MTcwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H91" t="n">
-        <v>95</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>NDllNDg4ZDAtZjJkNi00ZDcwLWJmMzMtNTIxMzJjMmEyMzJmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>2</v>
-      </c>
-      <c r="C92" t="n">
-        <v>1289</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="n">
-        <v>10</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>NjliMThkYjktMTc0Yy00OTg4LTg3OWMtNzEyZThiNjgyM2QzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
-        <v>6445</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>OTI4NWJmNDgtODU3Yi00NzAxLWJlZTgtNzA4NmVhYjZiZDNhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>10</v>
-      </c>
-      <c r="C93" t="n">
-        <v>42</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="n">
-        <v>10</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>MjFjZDdjOWYtMWMyZS00YmU2LWEyYjAtOWZlMjMyM2I0ZmY3OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H93" t="n">
-        <v>4.2e+16</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OTMyOTYwZTktMDBhZS00MTg0LWFkY2QtM2YyZTI2YTA2MGRiOjU3MDE2</t>
+          <t>MTU2MjFmZWMtYWZjYi00MTg4LThjMmItNTM5ZWExYmYyYjM2OjU3MDE2</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>1225</v>
+        <v>350</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
@@ -6929,15 +6933,15 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ZDM1MmRmY2UtNTk2NC00Nzk1LTgzZDEtMTIxZDI0ZmI3MjkyOjU3MDE2</t>
+          <t>MzYyZjJjODUtNDVjYS00NmU3LWEwYzUtMzhmZDc3ZjM5NTc0OjU3MDE2</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1225</v>
+        <v>350</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6949,14 +6953,14 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OTVkNjI2ZmMtZGE1NC00NmE4LWExOTMtZjE0ODJmYjZiNzQ5OjU3MDE2</t>
+          <t>MjdkOWFjYmEtM2RiMi00NjA5LWE5ZjQtMDc0MmQyOThiNzk5OjU3MDE2</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C95" t="n">
-        <v>1.1895e+16</v>
+        <v>168</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
@@ -6969,11 +6973,11 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>YzM4NzY3MzktYzQzZS00Zjk3LTgxYjQtMzAxZWE0ZTk3NWY0OjU3MDE2</t>
+          <t>MWU3ZGQ4MmMtYTg0Zi00ZDM2LWIxNDgtNjBhZDljYjYwZTliOjU3MDE2</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1.1895e+16</v>
+        <v>8400000000000001</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -6989,20 +6993,16 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>YWI3ZTg3NDUtMzNmNi00ZjExLTg3ZWUtZjExNzBkOGFlNDFkOjU3MDE2</t>
+          <t>Mzk5MTdiNmEtZmE3Ni00NWExLWFiODctOTIwNTY4YmViNGMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>2</v>
       </c>
       <c r="C96" t="n">
-        <v>700</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
         <v>10</v>
       </c>
@@ -7013,15 +7013,15 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>OGEzODdhOTUtNmU2Ni00NWQ0LWFhMzgtNzQzMGI2MWY4MTcwOjU3MDE2</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>350</v>
+        <v>95</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -7033,14 +7033,14 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ZDU3OGQ2MTktZGJkYy00YjEyLTkzMzItNTExYTlkYjlkZTVmOjU3MDE2</t>
+          <t>NDllNDg4ZDAtZjJkNi00ZDcwLWJmMzMtNTIxMzJjMmEyMzJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97" t="n">
-        <v>12525</v>
+        <v>1289</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
@@ -7053,11 +7053,11 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>NTViMThiNzUtNWVmNy00ZDU1LWIxNzMtOGY5NjZhYTE4ZWMwOjU3MDE2</t>
+          <t>NjliMThkYjktMTc0Yy00OTg4LTg3OWMtNzEyZThiNjgyM2QzOjU3MDE2</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>12525</v>
+        <v>6445</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -7073,71 +7073,71 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
+          <t>OTI4NWJmNDgtODU3Yi00NzAxLWJlZTgtNzA4NmVhYjZiZDNhOjU3MDE2</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C98" t="n">
-        <v>350</v>
+        <v>42</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>MjFjZDdjOWYtMWMyZS00YmU2LWEyYjAtOWZlMjMyM2I0ZmY3OjU3MDE2</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>350</v>
+        <v>4.2e+16</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
+          <t>OTMyOTYwZTktMDBhZS00MTg0LWFkY2QtM2YyZTI2YTA2MGRiOjU3MDE2</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>2073</v>
+        <v>1225</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>ZDM1MmRmY2UtNTk2NC00Nzk1LTgzZDEtMTIxZDI0ZmI3MjkyOjU3MDE2</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>2073</v>
+        <v>1225</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7146,38 +7146,38 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
+          <t>OTVkNjI2ZmMtZGE1NC00NmE4LWExOTMtZjE0ODJmYjZiNzQ5OjU3MDE2</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>7375</v>
+        <v>1.1895e+16</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>YzM4NzY3MzktYzQzZS00Zjk3LTgxYjQtMzAxZWE0ZTk3NWY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>7375</v>
+        <v>1.1895e+16</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7186,47 +7186,51 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
+          <t>YWI3ZTg3NDUtMzNmNi00ZjExLTg3ZWUtZjExNzBkOGFlNDFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="D101" t="inlineStr"/>
+        <v>700</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E101" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>8399999999999999</v>
+        <v>350</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -960,7 +960,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,50 +487,55 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>canceledAt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>approvedBy</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>createdBy</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>approvedSignature</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>order.id</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>discount.type</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>discount.value</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>discount.total</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>customer.id</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>status_original</t>
         </is>
@@ -614,43 +619,44 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>2025-11-11T16:06:07.949Z</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>NTYyNjA5ODctODA0MS00ODJlLWE1MTQtOTY0ZTQyZWRjOTYwOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>NDgyMzQxODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -698,52 +704,53 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Edina K O Mishima</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/1774f003-3175-4be8-801c-c7e958af19a8/signatures/650d7c22-e91c-4757-9ac9-9ad5beab0def.png</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2025-11-11T15:48:38.327Z</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>OTRkZmU3YjYtNDc4OC00OWJlLTk2OWMtYmQ5Y2Q4ZWRiMTY3OjU3MDE2</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>NDgzNDgwNzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -796,43 +803,44 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>2025-11-05T13:06:35.085Z</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>ZWMwNWE3NTgtODkyOC00ZjE5LWI0YTgtYjY0NmYwMDY2OGIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>NDE2MTc1Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -881,43 +889,44 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-12-11T21:29:54.203Z</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>NDE3MTYzNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -970,39 +979,40 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>2026-01-30T18:45:35.907Z</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>NDM1ODE3Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1058,40 +1068,45 @@
           <t>2026-01-22T14:57:37.000Z</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-01-22T14:57:37.000Z</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2026-01-22T14:40:07.831Z</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>canceled</t>
         </is>
@@ -1140,43 +1155,44 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>IRACILDA LOPES</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2024-08-07T17:45:02.123Z</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>ZDM4ZDY1NjMtN2E5Yy00ZDQ3LWFlMDktYzUwYzk4NDQ4NWY1OjU3MDE2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>MzMxMDM0OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1228,48 +1244,49 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Rafael Machado Barboza</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/2a7e8c69-1223-41d3-967d-474788d2fb01/signatures/51c1ade7-ff37-4ee9-b84d-46ee75381607.png</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2025-08-28T15:35:41.479Z</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1326,43 +1343,44 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>2025-12-02T21:20:54.686Z</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>MzI2OTMyNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1411,43 +1429,44 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>2025-10-02T21:19:25.794Z</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>OGUzZjA5OGMtMTdlNy00MDY3LTllYjQtMzhmMWNhZGM4NjNmOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>NDcxNTkzODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1500,39 +1519,40 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>2026-01-20T19:19:08.741Z</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>NDM1ODE3Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1588,52 +1608,53 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Joana D’Arc Oliveira </t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/336279a3-e397-43dd-b3ef-8d0f677e97af/signatures/e23e6b48-ded8-4f36-a055-55d66d4bbb0d.png</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>2025-09-29T15:17:10.234Z</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>MzM3ODI5ODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1682,43 +1703,44 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>2025-09-29T18:42:56.833Z</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1767,43 +1789,44 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>2025-09-29T18:38:37.635Z</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1852,43 +1875,44 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>2025-10-08T21:12:33.362Z</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>OTUxMWZiNzEtYjliOC00NTg4LWE5MTAtZmI2ZmQxZmZlZmNlOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>NDgzNDc2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1942,43 +1966,44 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>2025-12-12T16:00:42.963Z</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>OTYwNmY5MTktMmQxYi00NzI2LTg3MTYtZTJmMGE1MjE2NjFiOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>MzMxMDI2Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2033,43 +2058,44 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>2025-12-17T21:33:20.182Z</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>ODAxNDQ5MTMtNDYwMi00MjhmLWE1MWUtMWY1Y2I5NGIxY2Y1OjU3MDE2</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2118,43 +2144,44 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>2025-11-07T16:26:09.914Z</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>NDE3MTYzNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2207,43 +2234,44 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>2025-12-08T20:11:36.676Z</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>M2EzOTI5YTItODc3Zi00NTJlLTk1NDktMmU5YWRiMWMwZmQ1OjU3MDE2</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>NDgzNTU4Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2300,43 +2328,44 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
         <is>
           <t>2025-10-10T13:07:18.487Z</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>NDgyMzMyODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2397,43 +2426,44 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
         <is>
           <t>2025-11-17T15:14:20.735Z</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>MzI2OTMyNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>refused</t>
         </is>
@@ -2487,43 +2517,44 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
         <is>
           <t>2025-11-18T21:53:35.934Z</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>NjYwZjY1NTAtNjFmZS00N2NmLTlmZTktMzY2ZWVjNmViZGJmOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>NTgwMDkyOTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2588,39 +2619,40 @@
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
         <is>
           <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2677,39 +2709,40 @@
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
         <is>
           <t>RAFAEL BARBOZA</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
         <is>
           <t>2025-08-08T18:27:17.728Z</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2767,43 +2800,44 @@
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
         <is>
           <t>2025-12-09T20:21:45.714Z</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>MzIyOGRmMDAtMThlNi00NTc3LTk2MzctYmVjM2QxYmZlOWYwOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>NTg1NDM3Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2855,48 +2889,49 @@
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>douglas simao</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/6b2b07ff-cb70-450b-bc03-538da26b5fb0/signatures/82045e1d-cc6f-45af-a3f3-2c6a0906455d.png</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>2025-12-01T12:28:02.404Z</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>NDUwNzM2Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2949,43 +2984,44 @@
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
         <is>
           <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3038,43 +3074,44 @@
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
         <is>
           <t>2025-12-04T15:21:12.082Z</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Y2NjZDRjMTgtOWYwOC00YjUwLWFiNzktOGU0NGNhZTQzMTg3OjU3MDE2</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>MzUzMTEwNTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>expired</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,6 +536,11 @@
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>location.id</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>status_original</t>
         </is>
@@ -658,6 +663,11 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>NmFiMDUyZTMtMmRkMi00NWYwLWI1YzAtNzI5N2NmMGJiMzZhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -752,6 +762,11 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>NGNlYTU1YmYtMjg4My00OWI2LWE5YjEtNGEzNTNmZWU3MzZhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>approved</t>
         </is>
       </c>
@@ -842,6 +857,11 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>ZDg5NzUyMzktNDc5NS00NDU2LTg0MmItMjZhZjE2MWI3MWUzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -928,6 +948,11 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>ZjZiNTJjY2UtNDFhMS00NjllLTkyNDEtMjIzYmY5ODE2NmJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -1014,6 +1039,11 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>ZDBlYTE4ZjgtNTRlNS00YjQ2LWIwZDEtZmM2MDc4ZTFhYjY1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -1107,6 +1137,11 @@
         </is>
       </c>
       <c r="V7" t="inlineStr">
+        <is>
+          <t>YmEwMmQ1NzItYmIwMi00NTAxLWI4NWYtYmZiODY3NjIwZmRhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>canceled</t>
         </is>
@@ -1192,7 +1227,8 @@
           <t>MzMxMDM0OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1287,6 +1323,11 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>NWY5N2U0ZjYtNjA5Zi00YTkzLWE2ZmQtNjI2YmFhOTU1Y2UzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1382,6 +1423,11 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>MWUzYmI1OWItNmZiNC00ODg1LTg0ODktOTlmY2IyZWYxNWIxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -1468,6 +1514,11 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>MzQwNDRlN2UtMzgxYi00Nzc5LTk1MGItYTY3ODczZDg4NWM0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -1554,6 +1605,11 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>ZDBlYTE4ZjgtNTRlNS00YjQ2LWIwZDEtZmM2MDc4ZTFhYjY1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -1655,6 +1711,11 @@
         </is>
       </c>
       <c r="V13" t="inlineStr">
+        <is>
+          <t>MjU3OWZlNzYtYWVlNC00ODU0LWEyYTUtNDdkMWI2ZGY5ZDlmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1742,6 +1803,11 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -1828,6 +1894,11 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -1914,6 +1985,11 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>ZThkYWNiNmItMDliOS00Y2Y0LTgyNjgtOGU5OTk4NzQ3MmNkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -2005,6 +2081,11 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>ZWFiZTI5NDgtMzY0Ny00ODVkLThmNjEtODhjMGI2N2Q4Nzk2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -2097,6 +2178,11 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>ZTU1NzI4MzEtZTkzNS00ZWIzLTk4MTktMGE3MTZhOTE1NDZlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -2183,6 +2269,11 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>ZjZiNTJjY2UtNDFhMS00NjllLTkyNDEtMjIzYmY5ODE2NmJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -2273,6 +2364,11 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>NTk1Y2ZkMTYtMTk4YS00OTE4LWI5YzMtZjcwMTliOTdlNDVjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -2367,6 +2463,11 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
+          <t>NTg2M2M0ZTEtMThhNC00Y2YyLWFhNDktYTViMTdhYzE0MmZmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -2464,6 +2565,11 @@
         </is>
       </c>
       <c r="V22" t="inlineStr">
+        <is>
+          <t>MWUzYmI1OWItNmZiNC00ODg1LTg0ODktOTlmY2IyZWYxNWIxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
         <is>
           <t>refused</t>
         </is>
@@ -2555,6 +2661,11 @@
         </is>
       </c>
       <c r="V23" t="inlineStr">
+        <is>
+          <t>YTg3MTBjZDAtMzUwOC00OWNmLWIwMTAtMzMwNGVkOTA5ZWI0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2654,6 +2765,11 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
+          <t>NTU4NTRiMjItMTA0Yi00ZDEzLThiMDktNzdjYzcxMTFmNzU5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -2744,6 +2860,11 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
+          <t>NzE0ZTQzMTctOWNiOC00OTI2LTgyOTItOWY5NzYxZDE3OGQxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -2839,6 +2960,11 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
+          <t>M2NhMmM5M2MtNWIwNi00OWQwLWFmODgtYTQzNmJiOTUyM2EzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -2932,6 +3058,11 @@
         </is>
       </c>
       <c r="V27" t="inlineStr">
+        <is>
+          <t>ZjBjMzdjOTgtNWY3Yi00ZGQ5LTgwNTktMDZkMjI4YTAzYTAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3023,6 +3154,11 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
+          <t>OTNhMDBkOGItMzEyYy00MzVkLTlmYzItY2I4NWU2ZTQ5MzU5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
@@ -3112,6 +3248,11 @@
         </is>
       </c>
       <c r="V29" t="inlineStr">
+        <is>
+          <t>NTM2Nzc5ZjUtZjA3MS00NzY0LTkyNmMtNzQwNmNlZDgzZjEwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
         <is>
           <t>expired</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -1227,7 +1227,11 @@
           <t>MzMxMDM0OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>MDIzNDM2N2QtZGJmOS00YjhlLTk2ZjUtZWE2N2NlMGVhYjljOjU3MDE2</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>expired</t>
